--- a/Backend/Website/Nodebackend/scripts/automatic_report_download/companies_list.xlsx
+++ b/Backend/Website/Nodebackend/scripts/automatic_report_download/companies_list.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">Number of
 Shares</t>
@@ -62,63 +62,6 @@
     <t xml:space="preserve">Done</t>
   </si>
   <si>
-    <t xml:space="preserve">Zalando SE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://en.zalando.de/?_rfl=de</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://corporate.zalando.com/en/our-impact/downloads-and-contact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online retailing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excluded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alstria Office REIT-AG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://alstria.de/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://alstria.com/sustainability/#reports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AOX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aroundtown S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.aroundtown.de/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.aroundtown.de/sustainability/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luxemburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AT1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bechtle AG</t>
   </si>
   <si>
@@ -150,7 +93,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -193,22 +136,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <u val="single"/>
-      <sz val="10"/>
-      <color rgb="FF1155CC"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <u val="single"/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -265,7 +192,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
+  <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -289,11 +216,8 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -362,35 +286,18 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -416,7 +323,7 @@
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF1155CC"/>
+      <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -3817,146 +3724,46 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="C2" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="11" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-    </row>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+    </row>
+    <row r="1048474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -4058,10 +3865,6 @@
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" location="reports" display="https://alstria.com/sustainability/#reports"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://www.aroundtown.de/sustainability/"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
